--- a/proofs/out/itil/software-development-and-management/version-records/versions.xlsx
+++ b/proofs/out/itil/software-development-and-management/version-records/versions.xlsx
@@ -413,77 +413,672 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>meeting</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>codename</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>releaser</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>commits</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tsc-2024-01-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Richard, Ulises did a release for Node.js 20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>22.23.2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tsc-2024-01-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ruy, concerned it’s too much scope to pull into the runtime, Ruy, maybe adding other package managers to other containers might be a better way than building into the runtime Itself. Anecdotal correlation: Yarn v1 is currently shipped with our Docker image and it’s also the leading package manager s</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>22.23.1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Richard, a bit worried if we discuss backporting globs to Node.js 20, seems like we have already pulled back more than normal due to require esm which is good, but other things are being proposed just because we are doing a SemVer minor. Want to be careful about what we pull into 20.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>22.23.0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tsc-2025-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chengzhong has identified issue related to workers planning to submit patch to v8</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>22.22.3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>22.22.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>marco-ippolito</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.21.1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.21.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.20.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>richardlau</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.19.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.18.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.17.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22.17.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22.16.0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.15.1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>22.14.0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>aduh95</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22.13.1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RafaelGSS</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22.13.0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ruyadorno</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22.12.0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ruyadorno</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22.11.0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jod</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LTS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>richardlau</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
